--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8555"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="zone" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">zone!$G$1:$G$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="86">
   <si>
     <t>code</t>
   </si>
@@ -71,13 +74,13 @@
     <t>del_dtimes</t>
   </si>
   <si>
-    <t>ML</t>
-  </si>
-  <si>
-    <t>MotherLand</t>
-  </si>
-  <si>
-    <t>country</t>
+    <t>BOLI</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
   <si>
     <t>eng</t>
@@ -86,97 +89,205 @@
     <t>t</t>
   </si>
   <si>
-    <t>System</t>
+    <t>admin</t>
   </si>
   <si>
     <t>f</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
-    <t>Vega</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>ML/VA</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>Arcturus</t>
-  </si>
-  <si>
-    <t>ML/AS</t>
-  </si>
-  <si>
-    <t>RL</t>
-  </si>
-  <si>
-    <t>Rigel</t>
-  </si>
-  <si>
-    <t>ML/RL</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Murraya</t>
-  </si>
-  <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>ML/VA/MA</t>
-  </si>
-  <si>
-    <t>NS</t>
-  </si>
-  <si>
-    <t>Narcissus</t>
-  </si>
-  <si>
-    <t>ML/VA/NS</t>
-  </si>
-  <si>
-    <t>PS</t>
-  </si>
-  <si>
-    <t>Pandanus</t>
-  </si>
-  <si>
-    <t>ML/AS/PS</t>
-  </si>
-  <si>
-    <t>SM</t>
-  </si>
-  <si>
-    <t>Stramonium</t>
-  </si>
-  <si>
-    <t>ML/AS/SM</t>
-  </si>
-  <si>
-    <t>PW</t>
-  </si>
-  <si>
-    <t>Periwinkle</t>
-  </si>
-  <si>
-    <t>ML/AS/PW</t>
-  </si>
-  <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>Hollyhock</t>
-  </si>
-  <si>
-    <t>ML/RL/HH</t>
+    <t>BENI</t>
+  </si>
+  <si>
+    <t>Beni</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>BOLI/BENI</t>
+  </si>
+  <si>
+    <t>CHUQ</t>
+  </si>
+  <si>
+    <t>Chuquisaca</t>
+  </si>
+  <si>
+    <t>BOLI/CHUQ</t>
+  </si>
+  <si>
+    <t>COCH</t>
+  </si>
+  <si>
+    <t>Cochabamba</t>
+  </si>
+  <si>
+    <t>BOLI/COCH</t>
+  </si>
+  <si>
+    <t>LAPA</t>
+  </si>
+  <si>
+    <t>La Paz</t>
+  </si>
+  <si>
+    <t>BOLI/LAPA</t>
+  </si>
+  <si>
+    <t>ORUR</t>
+  </si>
+  <si>
+    <t>Oruro</t>
+  </si>
+  <si>
+    <t>BOLI/ORUR</t>
+  </si>
+  <si>
+    <t>PAND</t>
+  </si>
+  <si>
+    <t>Pando</t>
+  </si>
+  <si>
+    <t>BOLI/PAND</t>
+  </si>
+  <si>
+    <t>POTO</t>
+  </si>
+  <si>
+    <t>Potosí</t>
+  </si>
+  <si>
+    <t>BOLI/POTO</t>
+  </si>
+  <si>
+    <t>SANT</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>BOLI/SANT</t>
+  </si>
+  <si>
+    <t>TARI</t>
+  </si>
+  <si>
+    <t>Tarija</t>
+  </si>
+  <si>
+    <t>BOLI/TARI</t>
+  </si>
+  <si>
+    <t>CERC</t>
+  </si>
+  <si>
+    <t>Cercado</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/CERC</t>
+  </si>
+  <si>
+    <t>VACA</t>
+  </si>
+  <si>
+    <t>Vaca Díez</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/VACA</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>José Ballivián</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/JOSE</t>
+  </si>
+  <si>
+    <t>YACU</t>
+  </si>
+  <si>
+    <t>Yacuma</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/YACU</t>
+  </si>
+  <si>
+    <t>MOXO</t>
+  </si>
+  <si>
+    <t>Moxos</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/MOXO</t>
+  </si>
+  <si>
+    <t>MARB</t>
+  </si>
+  <si>
+    <t>Marban</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/MARB</t>
+  </si>
+  <si>
+    <t>MAMO</t>
+  </si>
+  <si>
+    <t>Mamoré</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/MAMO</t>
+  </si>
+  <si>
+    <t>ITEN</t>
+  </si>
+  <si>
+    <t>Iténez</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/ITEN</t>
+  </si>
+  <si>
+    <t>TRIN</t>
+  </si>
+  <si>
+    <t>Trinidad</t>
+  </si>
+  <si>
+    <t>Commune</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/CERC/TRIN</t>
+  </si>
+  <si>
+    <t>SANJ</t>
+  </si>
+  <si>
+    <t>San Javier</t>
+  </si>
+  <si>
+    <t>BOLI/BENI/CERC/SANJ</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>Departamento</t>
+  </si>
+  <si>
+    <t>Provincia</t>
+  </si>
+  <si>
+    <t>Comuna</t>
   </si>
 </sst>
 </file>
@@ -189,13 +300,19 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -662,139 +779,148 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
@@ -1332,29 +1458,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="3" width="10" style="1"/>
+    <col min="4" max="4" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.8888888888889" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1380,22 +1513,23 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H2" t="s">
@@ -1404,33 +1538,33 @@
       <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1">
-        <v>45526.6049657581</v>
+      <c r="J2" s="4">
+        <v>45667.2624203424</v>
       </c>
       <c r="M2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H3" t="s">
@@ -1439,33 +1573,33 @@
       <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="1">
-        <v>45526.6049657581</v>
+      <c r="J3" s="4">
+        <v>45667.2624203424</v>
       </c>
       <c r="M3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H4" t="s">
@@ -1474,33 +1608,33 @@
       <c r="I4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="1">
-        <v>45526.6049657581</v>
+      <c r="J4" s="4">
+        <v>45667.2624203424</v>
       </c>
       <c r="M4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H5" t="s">
@@ -1509,224 +1643,1275 @@
       <c r="I5" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="1">
-        <v>45526.6049657581</v>
+      <c r="J5" s="4">
+        <v>45667.2624203424</v>
       </c>
       <c r="M5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="2">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="4">
+        <v>45667.2624203424</v>
+      </c>
+      <c r="M21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="4">
+        <v>45667.3040870091</v>
+      </c>
+      <c r="M22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="4">
+        <v>45667.3457536758</v>
+      </c>
+      <c r="M23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="4">
+        <v>45667.3874203424</v>
+      </c>
+      <c r="M24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="2">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H25" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="4">
+        <v>45667.4290870091</v>
+      </c>
+      <c r="M25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H26" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="4">
+        <v>45667.4707536758</v>
+      </c>
+      <c r="M26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F6" t="s">
+      <c r="B27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="4">
+        <v>45667.5124203424</v>
+      </c>
+      <c r="M27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="4">
+        <v>45667.5540870091</v>
+      </c>
+      <c r="M28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="2">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="4">
+        <v>45667.5957536758</v>
+      </c>
+      <c r="M29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="4">
+        <v>45667.6374203424</v>
+      </c>
+      <c r="M30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="2">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="4">
+        <v>45667.6790870091</v>
+      </c>
+      <c r="M31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="2">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7">
+      <c r="G32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="4">
+        <v>45667.7207536758</v>
+      </c>
+      <c r="M32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="2">
         <v>2</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8">
+      <c r="G33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="4">
+        <v>45667.7624203424</v>
+      </c>
+      <c r="M33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9">
+      <c r="D34" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="4">
+        <v>45667.8040870091</v>
+      </c>
+      <c r="M34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="2">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10">
+      <c r="D35" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="4">
+        <v>45667.8457536758</v>
+      </c>
+      <c r="M35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="2">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11">
+      <c r="D36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="4">
+        <v>45667.8874203424</v>
+      </c>
+      <c r="M36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2">
         <v>2</v>
       </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="4">
+        <v>45667.9290870091</v>
+      </c>
+      <c r="M37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="2">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H38" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="4">
+        <v>45667.9707536758</v>
+      </c>
+      <c r="M38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="2">
+        <v>2</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="4">
+        <v>45668.0124203424</v>
+      </c>
+      <c r="M39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="2">
+        <v>3</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="1">
-        <v>45526.6049657581</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="G40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="4">
+        <v>45668.0540870091</v>
+      </c>
+      <c r="M40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="2">
+        <v>3</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="4">
+        <v>45668.0957536758</v>
+      </c>
+      <c r="M41" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="G1:G21" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
